--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,112 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
-  <si>
-    <t>ArrowMakeupGuideUIForm.go</t>
-  </si>
-  <si>
-    <t>Let's go</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earm the game, Play  for rewards</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip2</t>
-  </si>
-  <si>
-    <t>Ready to earn money!</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.Title</t>
-  </si>
-  <si>
-    <t>Game Guide</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.account</t>
-  </si>
-  <si>
-    <t>Account</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.continue</t>
-  </si>
-  <si>
-    <t>Continue</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.payment</t>
-  </si>
-  <si>
-    <t>Payment Channel</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.rebind</t>
-  </si>
-  <si>
-    <t>Rebind</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.tips</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>ArrowMakeupOrdemUIForm.record</t>
-  </si>
-  <si>
-    <t>Withdraw Record</t>
-  </si>
-  <si>
-    <t>ArrowMakeupTipsUIForm.Text_Title</t>
-  </si>
-  <si>
-    <t>Withdraw instructions</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.makeup</t>
-  </si>
-  <si>
-    <t>Withdraw</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.play</t>
-  </si>
-  <si>
-    <t>Go To Play</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.title</t>
-  </si>
-  <si>
-    <t>Withdrawal Requirements</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.curBankInfo</t>
-  </si>
-  <si>
-    <t>Please select a payment method.</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Withdrawal Ratio: </t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.tile</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.title_text</t>
-  </si>
-  <si>
-    <t>Balance</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -201,22 +96,10 @@
     <t>Please select an arrow to erase</t>
   </si>
   <si>
-    <t>ArrowMazeUIForm.ItemAutoRemoveFail</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>ArrowMazeUIForm.LevelTxt</t>
   </si>
   <si>
     <t>Level {0}</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.makeuptxt</t>
-  </si>
-  <si>
-    <t>Collect {0} to withdraw!</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -232,6 +115,9 @@
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.Continue</t>
+  </si>
+  <si>
+    <t>Continue</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.NextLevel</t>
@@ -256,45 +142,6 @@
   </si>
   <si>
     <t>Congratulations</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.claim</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.Notchanks</t>
-  </si>
-  <si>
-    <t>No,thanks</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardUIForm.check</t>
-  </si>
-  <si>
-    <t>Check Card</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.Confirm</t>
-  </si>
-  <si>
-    <t>Confirm</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>Please enter your {0} account</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title</t>
-  </si>
-  <si>
-    <t>Withdrawal Method</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title_1</t>
-  </si>
-  <si>
-    <t>Platform</t>
   </si>
   <si>
     <t>ArrowSettingController.OFF</t>
@@ -478,6 +325,12 @@
   </si>
   <si>
     <t>Collect another {0} to withdraw</t>
+  </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t>Win {0} levels!</t>
   </si>
 </sst>
 </file>
@@ -1441,27 +1294,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1469,43 +1322,43 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1513,42 +1366,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -1556,96 +1389,12 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1658,6 +1407,286 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -10453,2242 +10482,6 @@
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1138"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1139">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1140">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1141">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1142">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1143">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1144">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1145">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1146">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1147">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1148">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1149">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1150">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1151">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1152">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1153">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1154">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1155">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1156">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1157">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1158">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1158"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1159">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1159"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1160">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1160"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A67" id="1161">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1161"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A68" id="1162">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1162"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1163">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1163"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1164">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -13015,11 +10808,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="39.737557547433" customWidth="1"/>
+    <col min="2" max="2" width="34.0738721575056" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -13173,7 +10966,7 @@
         <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -13272,385 +11065,151 @@
         <v>53</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
         <v>86</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1"/>
-      <c r="B67" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1"/>
-      <c r="B68" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1"/>
-      <c r="B69" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1"/>
-      <c r="B70" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -13663,7 +11222,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1250" name="A1">
+            <control shapeId="1095" r:id="rId1319" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13685,7 +11244,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1251" name="A2">
+            <control shapeId="1096" r:id="rId1320" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13707,7 +11266,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1252" name="A3">
+            <control shapeId="1097" r:id="rId1321" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13729,7 +11288,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1253" name="A4">
+            <control shapeId="1098" r:id="rId1322" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13751,7 +11310,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1254" name="A5">
+            <control shapeId="1099" r:id="rId1323" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13773,7 +11332,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1255" name="A6">
+            <control shapeId="1100" r:id="rId1324" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13795,7 +11354,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1256" name="A7">
+            <control shapeId="1101" r:id="rId1325" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13817,7 +11376,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1257" name="A8">
+            <control shapeId="1102" r:id="rId1326" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13839,7 +11398,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1258" name="A9">
+            <control shapeId="1103" r:id="rId1327" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13861,7 +11420,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1259" name="A10">
+            <control shapeId="1104" r:id="rId1328" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13883,7 +11442,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1260" name="A11">
+            <control shapeId="1105" r:id="rId1329" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13905,7 +11464,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1261" name="A12">
+            <control shapeId="1106" r:id="rId1330" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13927,7 +11486,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1262" name="A13">
+            <control shapeId="1107" r:id="rId1331" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13949,7 +11508,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1263" name="A14">
+            <control shapeId="1108" r:id="rId1332" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13971,7 +11530,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1264" name="A15">
+            <control shapeId="1109" r:id="rId1333" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13993,7 +11552,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1265" name="A16">
+            <control shapeId="1110" r:id="rId1334" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14015,7 +11574,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1266" name="A17">
+            <control shapeId="1111" r:id="rId1335" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14037,7 +11596,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1267" name="A18">
+            <control shapeId="1112" r:id="rId1336" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14059,7 +11618,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1268" name="A19">
+            <control shapeId="1113" r:id="rId1337" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14081,7 +11640,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1269" name="A20">
+            <control shapeId="1114" r:id="rId1338" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14103,7 +11662,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1270" name="A21">
+            <control shapeId="1115" r:id="rId1339" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14125,7 +11684,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1271" name="A22">
+            <control shapeId="1116" r:id="rId1340" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14147,7 +11706,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1272" name="A23">
+            <control shapeId="1117" r:id="rId1341" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14169,7 +11728,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1273" name="A24">
+            <control shapeId="1118" r:id="rId1342" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14191,7 +11750,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1274" name="A25">
+            <control shapeId="1119" r:id="rId1343" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14213,7 +11772,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1275" name="A26">
+            <control shapeId="1120" r:id="rId1344" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14235,7 +11794,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1276" name="A27">
+            <control shapeId="1121" r:id="rId1345" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14257,7 +11816,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1277" name="A28">
+            <control shapeId="1122" r:id="rId1346" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14279,7 +11838,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1278" name="A29">
+            <control shapeId="1123" r:id="rId1347" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14301,7 +11860,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1279" name="A30">
+            <control shapeId="1124" r:id="rId1348" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14323,7 +11882,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1280" name="A31">
+            <control shapeId="1125" r:id="rId1349" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14345,7 +11904,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1281" name="A32">
+            <control shapeId="1126" r:id="rId1350" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14367,7 +11926,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1282" name="A33">
+            <control shapeId="1127" r:id="rId1351" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14389,7 +11948,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1283" name="A34">
+            <control shapeId="1128" r:id="rId1352" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14411,7 +11970,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1284" name="A35">
+            <control shapeId="1129" r:id="rId1353" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14433,7 +11992,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1285" name="A36">
+            <control shapeId="1130" r:id="rId1354" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14455,7 +12014,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1286" name="A37">
+            <control shapeId="1131" r:id="rId1355" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14477,7 +12036,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1287" name="A38">
+            <control shapeId="1132" r:id="rId1356" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14499,7 +12058,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1288" name="A39">
+            <control shapeId="1133" r:id="rId1357" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14521,7 +12080,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1289" name="A40">
+            <control shapeId="1134" r:id="rId1358" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14543,7 +12102,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1290" name="A41">
+            <control shapeId="1135" r:id="rId1359" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14565,7 +12124,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1291" name="A42">
+            <control shapeId="1136" r:id="rId1360" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14587,7 +12146,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1292" name="A43">
+            <control shapeId="1137" r:id="rId1361" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14609,7 +12168,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1293" name="A44">
+            <control shapeId="1138" r:id="rId1362" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14629,578 +12188,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId1294" name="A45">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId1295" name="A46">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId1296" name="A47">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId1297" name="A48">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId1298" name="A49">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId1299" name="A50">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId1300" name="A51">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId1301" name="A52">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId1302" name="A53">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId1303" name="A54">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId1304" name="A55">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId1305" name="A56">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId1306" name="A57">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId1307" name="A58">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId1308" name="A59">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId1309" name="A60">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId1310" name="A61">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId1311" name="A62">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId1312" name="A63">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1158" r:id="rId1313" name="A64">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1159" r:id="rId1314" name="A65">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1160" r:id="rId1315" name="A66">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1161" r:id="rId1316" name="A67">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1162" r:id="rId1317" name="A68">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1163" r:id="rId1318" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId1319" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>Collect another {0} to withdraw</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>Cash Out</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -1385,6 +1391,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6764,6 +6774,182 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -6780,7 +6966,2243 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1095">
+            <xdr:cNvPr hidden="1" name="A1" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A3" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A4" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A5" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A6" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A7" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A8" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A9" id="1077">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A10" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A11" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A12" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A13" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A14" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A15" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1085">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1085"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1086">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1086"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1087">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1087"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1088">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1088"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1089">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1089"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1090">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6855,18 +9277,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1096">
+            <xdr:cNvPr hidden="1" name="A28" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6941,18 +9363,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1097">
+            <xdr:cNvPr hidden="1" name="A29" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -7027,18 +9449,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1098">
+            <xdr:cNvPr hidden="1" name="A30" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -7113,18 +9535,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1099">
+            <xdr:cNvPr hidden="1" name="A31" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -7199,18 +9621,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1100">
+            <xdr:cNvPr hidden="1" name="A32" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -7285,18 +9707,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1101">
+            <xdr:cNvPr hidden="1" name="A33" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -7371,18 +9793,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1102">
+            <xdr:cNvPr hidden="1" name="A34" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -7457,18 +9879,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1103">
+            <xdr:cNvPr hidden="1" name="A35" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -7543,18 +9965,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1104">
+            <xdr:cNvPr hidden="1" name="A36" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -7629,18 +10051,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1105">
+            <xdr:cNvPr hidden="1" name="A37" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -7715,18 +10137,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1106">
+            <xdr:cNvPr hidden="1" name="A38" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7801,18 +10223,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1107">
+            <xdr:cNvPr hidden="1" name="A39" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7887,18 +10309,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1108">
+            <xdr:cNvPr hidden="1" name="A40" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7973,18 +10395,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1109">
+            <xdr:cNvPr hidden="1" name="A41" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -8059,18 +10481,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1110">
+            <xdr:cNvPr hidden="1" name="A42" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -8145,18 +10567,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1111">
+            <xdr:cNvPr hidden="1" name="A43" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -8231,18 +10653,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1112">
+            <xdr:cNvPr hidden="1" name="A44" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -8317,2171 +10739,21 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1113">
+            <xdr:cNvPr hidden="1" name="A45" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1114">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1115">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1116">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1117">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1118">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1119">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1120">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1121">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1122">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1123">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1124">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1125">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1126">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1127">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1128">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1129">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1130">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1131">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1132">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1133">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1134">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1135">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1136">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1137">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1138">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -10808,7 +11080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -11212,6 +11484,15 @@
         <v>86</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11222,7 +11503,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1319" name="A1">
+            <control shapeId="1069" r:id="rId1362" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11244,7 +11525,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1320" name="A2">
+            <control shapeId="1070" r:id="rId1363" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11266,7 +11547,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1321" name="A3">
+            <control shapeId="1071" r:id="rId1364" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11288,7 +11569,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1322" name="A4">
+            <control shapeId="1072" r:id="rId1365" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11310,7 +11591,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1323" name="A5">
+            <control shapeId="1073" r:id="rId1366" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11332,7 +11613,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1324" name="A6">
+            <control shapeId="1074" r:id="rId1367" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11354,7 +11635,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1325" name="A7">
+            <control shapeId="1075" r:id="rId1368" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11376,7 +11657,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1326" name="A8">
+            <control shapeId="1076" r:id="rId1369" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11398,7 +11679,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1327" name="A9">
+            <control shapeId="1077" r:id="rId1370" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11420,7 +11701,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1328" name="A10">
+            <control shapeId="1078" r:id="rId1371" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11442,7 +11723,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1329" name="A11">
+            <control shapeId="1079" r:id="rId1372" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11464,7 +11745,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1330" name="A12">
+            <control shapeId="1080" r:id="rId1373" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11486,7 +11767,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1331" name="A13">
+            <control shapeId="1081" r:id="rId1374" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11508,7 +11789,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1332" name="A14">
+            <control shapeId="1082" r:id="rId1375" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11530,7 +11811,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1333" name="A15">
+            <control shapeId="1083" r:id="rId1376" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11552,7 +11833,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1334" name="A16">
+            <control shapeId="1084" r:id="rId1377" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11574,7 +11855,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1335" name="A17">
+            <control shapeId="1085" r:id="rId1378" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11596,7 +11877,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1336" name="A18">
+            <control shapeId="1086" r:id="rId1379" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11618,7 +11899,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1337" name="A19">
+            <control shapeId="1087" r:id="rId1380" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11640,7 +11921,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1338" name="A20">
+            <control shapeId="1088" r:id="rId1381" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11662,7 +11943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1339" name="A21">
+            <control shapeId="1089" r:id="rId1382" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11684,7 +11965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1340" name="A22">
+            <control shapeId="1090" r:id="rId1383" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11706,7 +11987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1341" name="A23">
+            <control shapeId="1091" r:id="rId1384" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11728,7 +12009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1342" name="A24">
+            <control shapeId="1092" r:id="rId1385" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11750,7 +12031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1343" name="A25">
+            <control shapeId="1093" r:id="rId1386" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11772,7 +12053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1344" name="A26">
+            <control shapeId="1094" r:id="rId1387" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11794,7 +12075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1345" name="A27">
+            <control shapeId="1095" r:id="rId1388" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11816,7 +12097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1346" name="A28">
+            <control shapeId="1096" r:id="rId1389" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11838,7 +12119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1347" name="A29">
+            <control shapeId="1097" r:id="rId1390" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11860,7 +12141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1348" name="A30">
+            <control shapeId="1098" r:id="rId1391" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11882,7 +12163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1349" name="A31">
+            <control shapeId="1099" r:id="rId1392" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11904,7 +12185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1350" name="A32">
+            <control shapeId="1100" r:id="rId1393" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11926,7 +12207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1351" name="A33">
+            <control shapeId="1101" r:id="rId1394" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11948,7 +12229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1352" name="A34">
+            <control shapeId="1102" r:id="rId1395" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11970,7 +12251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1353" name="A35">
+            <control shapeId="1103" r:id="rId1396" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11992,7 +12273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1354" name="A36">
+            <control shapeId="1104" r:id="rId1397" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12014,7 +12295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1355" name="A37">
+            <control shapeId="1105" r:id="rId1398" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12036,7 +12317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1356" name="A38">
+            <control shapeId="1106" r:id="rId1399" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12058,7 +12339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1357" name="A39">
+            <control shapeId="1107" r:id="rId1400" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12080,7 +12361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1358" name="A40">
+            <control shapeId="1108" r:id="rId1401" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12102,7 +12383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1359" name="A41">
+            <control shapeId="1109" r:id="rId1402" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12124,7 +12405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1360" name="A42">
+            <control shapeId="1110" r:id="rId1403" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12146,7 +12427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1361" name="A43">
+            <control shapeId="1111" r:id="rId1404" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12168,7 +12449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1362" name="A44">
+            <control shapeId="1112" r:id="rId1405" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12188,6 +12469,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1113" r:id="rId1406" name="A45">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>44</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -313,6 +313,18 @@
   </si>
   <si>
     <t>We regret that the exchange has failed.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>Please ensure that the PayPal account entered twice is consistent.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>Please enter the correct email format.</t>
   </si>
   <si>
     <t>MakeUpStep1</t>
@@ -1388,10 +1400,18 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6950,6 +6970,370 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -6966,179 +7350,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1069">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1070">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1071">
+            <xdr:cNvPr hidden="1" name="A1" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -7213,18 +7425,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1072">
+            <xdr:cNvPr hidden="1" name="A2" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -7299,18 +7511,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1073">
+            <xdr:cNvPr hidden="1" name="A3" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7385,18 +7597,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1074">
+            <xdr:cNvPr hidden="1" name="A4" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7471,18 +7683,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1075">
+            <xdr:cNvPr hidden="1" name="A5" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7557,18 +7769,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1076">
+            <xdr:cNvPr hidden="1" name="A6" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7643,18 +7855,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1077">
+            <xdr:cNvPr hidden="1" name="A7" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -7729,18 +7941,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1078">
+            <xdr:cNvPr hidden="1" name="A8" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -7815,18 +8027,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1079">
+            <xdr:cNvPr hidden="1" name="A9" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -7901,18 +8113,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1080">
+            <xdr:cNvPr hidden="1" name="A10" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -7987,18 +8199,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1081">
+            <xdr:cNvPr hidden="1" name="A11" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -8073,18 +8285,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1082">
+            <xdr:cNvPr hidden="1" name="A12" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8159,18 +8371,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1083">
+            <xdr:cNvPr hidden="1" name="A13" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8245,18 +8457,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1084">
+            <xdr:cNvPr hidden="1" name="A14" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8331,18 +8543,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1085">
+            <xdr:cNvPr hidden="1" name="A15" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8417,18 +8629,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1086">
+            <xdr:cNvPr hidden="1" name="A16" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8503,18 +8715,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1087">
+            <xdr:cNvPr hidden="1" name="A17" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8589,18 +8801,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1088">
+            <xdr:cNvPr hidden="1" name="A18" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8675,18 +8887,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1089">
+            <xdr:cNvPr hidden="1" name="A19" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -8761,18 +8973,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1090">
+            <xdr:cNvPr hidden="1" name="A20" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -8847,18 +9059,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1091">
+            <xdr:cNvPr hidden="1" name="A21" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -8933,18 +9145,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1092">
+            <xdr:cNvPr hidden="1" name="A22" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9019,18 +9231,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1093">
+            <xdr:cNvPr hidden="1" name="A23" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9105,18 +9317,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1094">
+            <xdr:cNvPr hidden="1" name="A24" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9191,18 +9403,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1095">
+            <xdr:cNvPr hidden="1" name="A25" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9277,18 +9489,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1096">
+            <xdr:cNvPr hidden="1" name="A26" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9363,18 +9575,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1097">
+            <xdr:cNvPr hidden="1" name="A27" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9449,18 +9661,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1098">
+            <xdr:cNvPr hidden="1" name="A28" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9535,18 +9747,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1099">
+            <xdr:cNvPr hidden="1" name="A29" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9621,18 +9833,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1100">
+            <xdr:cNvPr hidden="1" name="A30" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -9707,18 +9919,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1101">
+            <xdr:cNvPr hidden="1" name="A31" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -9793,18 +10005,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1102">
+            <xdr:cNvPr hidden="1" name="A32" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -9879,18 +10091,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1103">
+            <xdr:cNvPr hidden="1" name="A33" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -9965,18 +10177,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1104">
+            <xdr:cNvPr hidden="1" name="A34" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10051,18 +10263,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1105">
+            <xdr:cNvPr hidden="1" name="A35" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10137,18 +10349,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1106">
+            <xdr:cNvPr hidden="1" name="A36" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10223,18 +10435,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1107">
+            <xdr:cNvPr hidden="1" name="A37" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10309,18 +10521,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1108">
+            <xdr:cNvPr hidden="1" name="A38" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10395,18 +10607,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1109">
+            <xdr:cNvPr hidden="1" name="A39" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10481,18 +10693,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1110">
+            <xdr:cNvPr hidden="1" name="A40" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10567,18 +10779,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1111">
+            <xdr:cNvPr hidden="1" name="A41" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10653,18 +10865,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1112">
+            <xdr:cNvPr hidden="1" name="A42" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -10739,6 +10951,178 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A43" id="1113">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1113"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1114">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1114"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -10750,10 +11134,182 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1113">
+            <xdr:cNvPr hidden="1" name="A45" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1115"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1116">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1116"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1117">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1117"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11080,7 +11636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -11493,6 +12049,24 @@
         <v>88</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1"/>
+      <c r="B47" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11503,7 +12077,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId1362" name="A1">
+            <control shapeId="1071" r:id="rId1451" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11525,7 +12099,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId1363" name="A2">
+            <control shapeId="1072" r:id="rId1452" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11547,7 +12121,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId1364" name="A3">
+            <control shapeId="1073" r:id="rId1453" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11569,7 +12143,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1365" name="A4">
+            <control shapeId="1074" r:id="rId1454" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11591,7 +12165,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1366" name="A5">
+            <control shapeId="1075" r:id="rId1455" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11613,7 +12187,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1367" name="A6">
+            <control shapeId="1076" r:id="rId1456" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11635,7 +12209,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1368" name="A7">
+            <control shapeId="1077" r:id="rId1457" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11657,7 +12231,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1369" name="A8">
+            <control shapeId="1078" r:id="rId1458" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11679,7 +12253,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1370" name="A9">
+            <control shapeId="1079" r:id="rId1459" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11701,7 +12275,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1371" name="A10">
+            <control shapeId="1080" r:id="rId1460" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11723,7 +12297,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1372" name="A11">
+            <control shapeId="1081" r:id="rId1461" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11745,7 +12319,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1373" name="A12">
+            <control shapeId="1082" r:id="rId1462" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11767,7 +12341,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1374" name="A13">
+            <control shapeId="1083" r:id="rId1463" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11789,7 +12363,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1375" name="A14">
+            <control shapeId="1084" r:id="rId1464" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11811,7 +12385,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1376" name="A15">
+            <control shapeId="1085" r:id="rId1465" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11833,7 +12407,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1377" name="A16">
+            <control shapeId="1086" r:id="rId1466" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11855,7 +12429,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1378" name="A17">
+            <control shapeId="1087" r:id="rId1467" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11877,7 +12451,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1379" name="A18">
+            <control shapeId="1088" r:id="rId1468" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11899,7 +12473,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1380" name="A19">
+            <control shapeId="1089" r:id="rId1469" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11921,7 +12495,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1381" name="A20">
+            <control shapeId="1090" r:id="rId1470" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11943,7 +12517,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1382" name="A21">
+            <control shapeId="1091" r:id="rId1471" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11965,7 +12539,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1383" name="A22">
+            <control shapeId="1092" r:id="rId1472" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11987,7 +12561,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1384" name="A23">
+            <control shapeId="1093" r:id="rId1473" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12009,7 +12583,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1385" name="A24">
+            <control shapeId="1094" r:id="rId1474" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12031,7 +12605,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1386" name="A25">
+            <control shapeId="1095" r:id="rId1475" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12053,7 +12627,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1387" name="A26">
+            <control shapeId="1096" r:id="rId1476" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12075,7 +12649,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1388" name="A27">
+            <control shapeId="1097" r:id="rId1477" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12097,7 +12671,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1389" name="A28">
+            <control shapeId="1098" r:id="rId1478" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12119,7 +12693,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1390" name="A29">
+            <control shapeId="1099" r:id="rId1479" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12141,7 +12715,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1391" name="A30">
+            <control shapeId="1100" r:id="rId1480" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12163,7 +12737,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1392" name="A31">
+            <control shapeId="1101" r:id="rId1481" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12185,7 +12759,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1393" name="A32">
+            <control shapeId="1102" r:id="rId1482" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12207,7 +12781,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1394" name="A33">
+            <control shapeId="1103" r:id="rId1483" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12229,7 +12803,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1395" name="A34">
+            <control shapeId="1104" r:id="rId1484" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12251,7 +12825,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1396" name="A35">
+            <control shapeId="1105" r:id="rId1485" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12273,7 +12847,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1397" name="A36">
+            <control shapeId="1106" r:id="rId1486" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12295,7 +12869,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1398" name="A37">
+            <control shapeId="1107" r:id="rId1487" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12317,7 +12891,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1399" name="A38">
+            <control shapeId="1108" r:id="rId1488" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12339,7 +12913,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1400" name="A39">
+            <control shapeId="1109" r:id="rId1489" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12361,7 +12935,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1401" name="A40">
+            <control shapeId="1110" r:id="rId1490" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12383,7 +12957,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1402" name="A41">
+            <control shapeId="1111" r:id="rId1491" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12405,7 +12979,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1403" name="A42">
+            <control shapeId="1112" r:id="rId1492" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12427,7 +13001,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1404" name="A43">
+            <control shapeId="1113" r:id="rId1493" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12449,7 +13023,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1405" name="A44">
+            <control shapeId="1114" r:id="rId1494" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12471,7 +13045,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1406" name="A45">
+            <control shapeId="1115" r:id="rId1495" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12491,6 +13065,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1116" r:id="rId1496" name="A46">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1117" r:id="rId1497" name="A47">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Cash Out</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -1415,6 +1418,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7334,6 +7341,194 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7350,93 +7545,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1071">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1072">
+            <xdr:cNvPr hidden="1" name="A1" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -7511,18 +7620,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1073">
+            <xdr:cNvPr hidden="1" name="A2" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7597,18 +7706,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1074">
+            <xdr:cNvPr hidden="1" name="A3" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7683,18 +7792,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1075">
+            <xdr:cNvPr hidden="1" name="A4" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7769,18 +7878,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1076">
+            <xdr:cNvPr hidden="1" name="A5" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7855,18 +7964,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1077">
+            <xdr:cNvPr hidden="1" name="A6" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -7941,18 +8050,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1078">
+            <xdr:cNvPr hidden="1" name="A7" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -8027,18 +8136,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1079">
+            <xdr:cNvPr hidden="1" name="A8" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -8113,18 +8222,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1080">
+            <xdr:cNvPr hidden="1" name="A9" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -8199,18 +8308,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1081">
+            <xdr:cNvPr hidden="1" name="A10" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -8285,18 +8394,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1082">
+            <xdr:cNvPr hidden="1" name="A11" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8371,18 +8480,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1083">
+            <xdr:cNvPr hidden="1" name="A12" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8457,18 +8566,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1084">
+            <xdr:cNvPr hidden="1" name="A13" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8543,18 +8652,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1085">
+            <xdr:cNvPr hidden="1" name="A14" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8629,18 +8738,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1086">
+            <xdr:cNvPr hidden="1" name="A15" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8715,18 +8824,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1087">
+            <xdr:cNvPr hidden="1" name="A16" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8801,18 +8910,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1088">
+            <xdr:cNvPr hidden="1" name="A17" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8887,18 +8996,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1089">
+            <xdr:cNvPr hidden="1" name="A18" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -8973,18 +9082,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1090">
+            <xdr:cNvPr hidden="1" name="A19" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -9059,18 +9168,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1091">
+            <xdr:cNvPr hidden="1" name="A20" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9145,18 +9254,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1092">
+            <xdr:cNvPr hidden="1" name="A21" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9231,18 +9340,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1093">
+            <xdr:cNvPr hidden="1" name="A22" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9317,18 +9426,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1094">
+            <xdr:cNvPr hidden="1" name="A23" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9403,18 +9512,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1095">
+            <xdr:cNvPr hidden="1" name="A24" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9489,18 +9598,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1096">
+            <xdr:cNvPr hidden="1" name="A25" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9575,18 +9684,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1097">
+            <xdr:cNvPr hidden="1" name="A26" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9661,18 +9770,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1098">
+            <xdr:cNvPr hidden="1" name="A27" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9747,18 +9856,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1099">
+            <xdr:cNvPr hidden="1" name="A28" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9833,18 +9942,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1100">
+            <xdr:cNvPr hidden="1" name="A29" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -9919,18 +10028,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1101">
+            <xdr:cNvPr hidden="1" name="A30" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10005,18 +10114,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1102">
+            <xdr:cNvPr hidden="1" name="A31" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10091,18 +10200,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1103">
+            <xdr:cNvPr hidden="1" name="A32" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10177,18 +10286,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1104">
+            <xdr:cNvPr hidden="1" name="A33" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10263,18 +10372,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1105">
+            <xdr:cNvPr hidden="1" name="A34" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10349,18 +10458,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1106">
+            <xdr:cNvPr hidden="1" name="A35" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10435,18 +10544,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1107">
+            <xdr:cNvPr hidden="1" name="A36" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10521,18 +10630,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1108">
+            <xdr:cNvPr hidden="1" name="A37" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10607,18 +10716,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1109">
+            <xdr:cNvPr hidden="1" name="A38" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10693,18 +10802,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1110">
+            <xdr:cNvPr hidden="1" name="A39" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10779,18 +10888,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1111">
+            <xdr:cNvPr hidden="1" name="A40" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10865,18 +10974,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1112">
+            <xdr:cNvPr hidden="1" name="A41" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -10951,18 +11060,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1113">
+            <xdr:cNvPr hidden="1" name="A42" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11037,18 +11146,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1114">
+            <xdr:cNvPr hidden="1" name="A43" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11123,18 +11232,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1115">
+            <xdr:cNvPr hidden="1" name="A44" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11209,18 +11318,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1116">
+            <xdr:cNvPr hidden="1" name="A45" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11295,6 +11404,92 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1117">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1117"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -11306,10 +11501,96 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1117">
+            <xdr:cNvPr hidden="1" name="A47" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1118"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1119">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1119"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11636,7 +11917,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -12064,7 +12345,16 @@
         <v>91</v>
       </c>
       <c r="C47" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1"/>
+      <c r="B48" s="0" t="s">
         <v>92</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -12077,7 +12367,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId1451" name="A1">
+            <control shapeId="1072" r:id="rId1497" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12099,7 +12389,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1452" name="A2">
+            <control shapeId="1073" r:id="rId1498" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12121,7 +12411,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1453" name="A3">
+            <control shapeId="1074" r:id="rId1499" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12143,7 +12433,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1454" name="A4">
+            <control shapeId="1075" r:id="rId1500" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12165,7 +12455,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1455" name="A5">
+            <control shapeId="1076" r:id="rId1501" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12187,7 +12477,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1456" name="A6">
+            <control shapeId="1077" r:id="rId1502" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12209,7 +12499,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1457" name="A7">
+            <control shapeId="1078" r:id="rId1503" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12231,7 +12521,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1458" name="A8">
+            <control shapeId="1079" r:id="rId1504" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12253,7 +12543,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1459" name="A9">
+            <control shapeId="1080" r:id="rId1505" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12275,7 +12565,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1460" name="A10">
+            <control shapeId="1081" r:id="rId1506" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12297,7 +12587,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1461" name="A11">
+            <control shapeId="1082" r:id="rId1507" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12319,7 +12609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1462" name="A12">
+            <control shapeId="1083" r:id="rId1508" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12341,7 +12631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1463" name="A13">
+            <control shapeId="1084" r:id="rId1509" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12363,7 +12653,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1464" name="A14">
+            <control shapeId="1085" r:id="rId1510" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12385,7 +12675,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1465" name="A15">
+            <control shapeId="1086" r:id="rId1511" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12407,7 +12697,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1466" name="A16">
+            <control shapeId="1087" r:id="rId1512" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12429,7 +12719,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1467" name="A17">
+            <control shapeId="1088" r:id="rId1513" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12451,7 +12741,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1468" name="A18">
+            <control shapeId="1089" r:id="rId1514" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12473,7 +12763,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1469" name="A19">
+            <control shapeId="1090" r:id="rId1515" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12495,7 +12785,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1470" name="A20">
+            <control shapeId="1091" r:id="rId1516" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12517,7 +12807,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1471" name="A21">
+            <control shapeId="1092" r:id="rId1517" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12539,7 +12829,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1472" name="A22">
+            <control shapeId="1093" r:id="rId1518" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12561,7 +12851,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1473" name="A23">
+            <control shapeId="1094" r:id="rId1519" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12583,7 +12873,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1474" name="A24">
+            <control shapeId="1095" r:id="rId1520" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12605,7 +12895,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1475" name="A25">
+            <control shapeId="1096" r:id="rId1521" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12627,7 +12917,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1476" name="A26">
+            <control shapeId="1097" r:id="rId1522" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12649,7 +12939,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1477" name="A27">
+            <control shapeId="1098" r:id="rId1523" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12671,7 +12961,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1478" name="A28">
+            <control shapeId="1099" r:id="rId1524" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12693,7 +12983,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1479" name="A29">
+            <control shapeId="1100" r:id="rId1525" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12715,7 +13005,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1480" name="A30">
+            <control shapeId="1101" r:id="rId1526" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12737,7 +13027,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1481" name="A31">
+            <control shapeId="1102" r:id="rId1527" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12759,7 +13049,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1482" name="A32">
+            <control shapeId="1103" r:id="rId1528" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12781,7 +13071,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1483" name="A33">
+            <control shapeId="1104" r:id="rId1529" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12803,7 +13093,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1484" name="A34">
+            <control shapeId="1105" r:id="rId1530" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12825,7 +13115,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1485" name="A35">
+            <control shapeId="1106" r:id="rId1531" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12847,7 +13137,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1486" name="A36">
+            <control shapeId="1107" r:id="rId1532" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12869,7 +13159,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1487" name="A37">
+            <control shapeId="1108" r:id="rId1533" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12891,7 +13181,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1488" name="A38">
+            <control shapeId="1109" r:id="rId1534" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12913,7 +13203,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1489" name="A39">
+            <control shapeId="1110" r:id="rId1535" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12935,7 +13225,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1490" name="A40">
+            <control shapeId="1111" r:id="rId1536" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12957,7 +13247,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1491" name="A41">
+            <control shapeId="1112" r:id="rId1537" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12979,7 +13269,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1492" name="A42">
+            <control shapeId="1113" r:id="rId1538" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13001,7 +13291,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1493" name="A43">
+            <control shapeId="1114" r:id="rId1539" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13023,7 +13313,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1494" name="A44">
+            <control shapeId="1115" r:id="rId1540" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13045,7 +13335,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1495" name="A45">
+            <control shapeId="1116" r:id="rId1541" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13067,7 +13357,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1496" name="A46">
+            <control shapeId="1117" r:id="rId1542" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13089,7 +13379,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1497" name="A47">
+            <control shapeId="1118" r:id="rId1543" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13109,6 +13399,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1119" r:id="rId1544" name="A48">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>Cash Out</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>Balance {0}=$1</t>
   </si>
   <si>
     <t>PrelevelUIForm.txtLevel</t>
@@ -1422,6 +1428,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7529,6 +7539,198 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7545,93 +7747,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1072">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1073">
+            <xdr:cNvPr hidden="1" name="A1" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7706,18 +7822,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1074">
+            <xdr:cNvPr hidden="1" name="A2" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7792,18 +7908,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1075">
+            <xdr:cNvPr hidden="1" name="A3" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7878,18 +7994,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1076">
+            <xdr:cNvPr hidden="1" name="A4" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7964,18 +8080,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1077">
+            <xdr:cNvPr hidden="1" name="A5" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -8050,18 +8166,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1078">
+            <xdr:cNvPr hidden="1" name="A6" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -8136,18 +8252,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1079">
+            <xdr:cNvPr hidden="1" name="A7" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -8222,18 +8338,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1080">
+            <xdr:cNvPr hidden="1" name="A8" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -8308,18 +8424,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1081">
+            <xdr:cNvPr hidden="1" name="A9" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -8394,18 +8510,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1082">
+            <xdr:cNvPr hidden="1" name="A10" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8480,18 +8596,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1083">
+            <xdr:cNvPr hidden="1" name="A11" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8566,18 +8682,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1084">
+            <xdr:cNvPr hidden="1" name="A12" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8652,18 +8768,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1085">
+            <xdr:cNvPr hidden="1" name="A13" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8738,18 +8854,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1086">
+            <xdr:cNvPr hidden="1" name="A14" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8824,18 +8940,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1087">
+            <xdr:cNvPr hidden="1" name="A15" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8910,18 +9026,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1088">
+            <xdr:cNvPr hidden="1" name="A16" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8996,18 +9112,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1089">
+            <xdr:cNvPr hidden="1" name="A17" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -9082,18 +9198,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1090">
+            <xdr:cNvPr hidden="1" name="A18" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -9168,18 +9284,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1091">
+            <xdr:cNvPr hidden="1" name="A19" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9254,18 +9370,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1092">
+            <xdr:cNvPr hidden="1" name="A20" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9340,18 +9456,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1093">
+            <xdr:cNvPr hidden="1" name="A21" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9426,18 +9542,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1094">
+            <xdr:cNvPr hidden="1" name="A22" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9512,18 +9628,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1095">
+            <xdr:cNvPr hidden="1" name="A23" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9598,18 +9714,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1096">
+            <xdr:cNvPr hidden="1" name="A24" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9684,18 +9800,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1097">
+            <xdr:cNvPr hidden="1" name="A25" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9770,18 +9886,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1098">
+            <xdr:cNvPr hidden="1" name="A26" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9856,18 +9972,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1099">
+            <xdr:cNvPr hidden="1" name="A27" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9942,18 +10058,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1100">
+            <xdr:cNvPr hidden="1" name="A28" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -10028,18 +10144,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1101">
+            <xdr:cNvPr hidden="1" name="A29" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10114,18 +10230,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1102">
+            <xdr:cNvPr hidden="1" name="A30" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10200,18 +10316,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1103">
+            <xdr:cNvPr hidden="1" name="A31" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10286,18 +10402,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1104">
+            <xdr:cNvPr hidden="1" name="A32" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10372,18 +10488,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1105">
+            <xdr:cNvPr hidden="1" name="A33" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10458,18 +10574,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1106">
+            <xdr:cNvPr hidden="1" name="A34" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10544,18 +10660,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1107">
+            <xdr:cNvPr hidden="1" name="A35" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10630,18 +10746,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1108">
+            <xdr:cNvPr hidden="1" name="A36" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10716,18 +10832,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1109">
+            <xdr:cNvPr hidden="1" name="A37" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10802,18 +10918,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1110">
+            <xdr:cNvPr hidden="1" name="A38" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10888,18 +11004,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1111">
+            <xdr:cNvPr hidden="1" name="A39" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10974,18 +11090,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1112">
+            <xdr:cNvPr hidden="1" name="A40" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -11060,18 +11176,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1113">
+            <xdr:cNvPr hidden="1" name="A41" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11146,18 +11262,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1114">
+            <xdr:cNvPr hidden="1" name="A42" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11232,18 +11348,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1115">
+            <xdr:cNvPr hidden="1" name="A43" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11318,18 +11434,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1116">
+            <xdr:cNvPr hidden="1" name="A44" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11404,18 +11520,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1117">
+            <xdr:cNvPr hidden="1" name="A45" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11490,18 +11606,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1118">
+            <xdr:cNvPr hidden="1" name="A46" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -11576,6 +11692,92 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1119">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1119"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -11587,10 +11789,96 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1119">
+            <xdr:cNvPr hidden="1" name="A48" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1120"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1121">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1121"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -11917,7 +12205,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -12345,16 +12633,25 @@
         <v>91</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>93</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -12367,7 +12664,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1497" name="A1">
+            <control shapeId="1073" r:id="rId1544" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12389,7 +12686,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1498" name="A2">
+            <control shapeId="1074" r:id="rId1545" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12411,7 +12708,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1499" name="A3">
+            <control shapeId="1075" r:id="rId1546" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12433,7 +12730,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1500" name="A4">
+            <control shapeId="1076" r:id="rId1547" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12455,7 +12752,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1501" name="A5">
+            <control shapeId="1077" r:id="rId1548" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12477,7 +12774,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1502" name="A6">
+            <control shapeId="1078" r:id="rId1549" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12499,7 +12796,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1503" name="A7">
+            <control shapeId="1079" r:id="rId1550" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12521,7 +12818,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1504" name="A8">
+            <control shapeId="1080" r:id="rId1551" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12543,7 +12840,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1505" name="A9">
+            <control shapeId="1081" r:id="rId1552" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12565,7 +12862,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1506" name="A10">
+            <control shapeId="1082" r:id="rId1553" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12587,7 +12884,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1507" name="A11">
+            <control shapeId="1083" r:id="rId1554" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12609,7 +12906,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1508" name="A12">
+            <control shapeId="1084" r:id="rId1555" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12631,7 +12928,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1509" name="A13">
+            <control shapeId="1085" r:id="rId1556" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12653,7 +12950,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1510" name="A14">
+            <control shapeId="1086" r:id="rId1557" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12675,7 +12972,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1511" name="A15">
+            <control shapeId="1087" r:id="rId1558" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12697,7 +12994,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1512" name="A16">
+            <control shapeId="1088" r:id="rId1559" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12719,7 +13016,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1513" name="A17">
+            <control shapeId="1089" r:id="rId1560" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12741,7 +13038,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1514" name="A18">
+            <control shapeId="1090" r:id="rId1561" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12763,7 +13060,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1515" name="A19">
+            <control shapeId="1091" r:id="rId1562" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12785,7 +13082,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1516" name="A20">
+            <control shapeId="1092" r:id="rId1563" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12807,7 +13104,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1517" name="A21">
+            <control shapeId="1093" r:id="rId1564" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12829,7 +13126,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1518" name="A22">
+            <control shapeId="1094" r:id="rId1565" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12851,7 +13148,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1519" name="A23">
+            <control shapeId="1095" r:id="rId1566" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12873,7 +13170,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1520" name="A24">
+            <control shapeId="1096" r:id="rId1567" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12895,7 +13192,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1521" name="A25">
+            <control shapeId="1097" r:id="rId1568" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12917,7 +13214,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1522" name="A26">
+            <control shapeId="1098" r:id="rId1569" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12939,7 +13236,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1523" name="A27">
+            <control shapeId="1099" r:id="rId1570" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12961,7 +13258,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1524" name="A28">
+            <control shapeId="1100" r:id="rId1571" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12983,7 +13280,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1525" name="A29">
+            <control shapeId="1101" r:id="rId1572" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13005,7 +13302,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1526" name="A30">
+            <control shapeId="1102" r:id="rId1573" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13027,7 +13324,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1527" name="A31">
+            <control shapeId="1103" r:id="rId1574" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13049,7 +13346,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1528" name="A32">
+            <control shapeId="1104" r:id="rId1575" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13071,7 +13368,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1529" name="A33">
+            <control shapeId="1105" r:id="rId1576" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13093,7 +13390,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1530" name="A34">
+            <control shapeId="1106" r:id="rId1577" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13115,7 +13412,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1531" name="A35">
+            <control shapeId="1107" r:id="rId1578" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13137,7 +13434,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1532" name="A36">
+            <control shapeId="1108" r:id="rId1579" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13159,7 +13456,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1533" name="A37">
+            <control shapeId="1109" r:id="rId1580" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13181,7 +13478,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1534" name="A38">
+            <control shapeId="1110" r:id="rId1581" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13203,7 +13500,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1535" name="A39">
+            <control shapeId="1111" r:id="rId1582" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13225,7 +13522,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1536" name="A40">
+            <control shapeId="1112" r:id="rId1583" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13247,7 +13544,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1537" name="A41">
+            <control shapeId="1113" r:id="rId1584" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13269,7 +13566,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1538" name="A42">
+            <control shapeId="1114" r:id="rId1585" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13291,7 +13588,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1539" name="A43">
+            <control shapeId="1115" r:id="rId1586" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13313,7 +13610,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1540" name="A44">
+            <control shapeId="1116" r:id="rId1587" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13335,7 +13632,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1541" name="A45">
+            <control shapeId="1117" r:id="rId1588" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13357,7 +13654,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1542" name="A46">
+            <control shapeId="1118" r:id="rId1589" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13379,7 +13676,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1543" name="A47">
+            <control shapeId="1119" r:id="rId1590" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13401,7 +13698,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1544" name="A48">
+            <control shapeId="1120" r:id="rId1591" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13421,6 +13718,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1121" r:id="rId1592" name="A49">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+  <si>
+    <t>AddBallsUIForm.ballTxt</t>
+  </si>
+  <si>
+    <t>+5 Balls</t>
+  </si>
+  <si>
+    <t>AddBallsUIForm.continueTxt</t>
+  </si>
+  <si>
+    <t>Continue?</t>
+  </si>
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -88,18 +100,6 @@
   </si>
   <si>
     <t>Revive</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.elimanateHit</t>
-  </si>
-  <si>
-    <t>Please select an arrow to erase</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.LevelTxt</t>
-  </si>
-  <si>
-    <t>Level {0}</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -207,6 +207,9 @@
     <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
   </si>
   <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
     <t>Enteraccountnumber</t>
   </si>
   <si>
@@ -267,6 +270,21 @@
     <t>Complete requirements to cash out.</t>
   </si>
   <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
@@ -309,6 +327,18 @@
     <t>Payment information saved successfully</t>
   </si>
   <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>Level {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.leveltxt</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
@@ -327,6 +357,18 @@
     <t>Please enter the correct email format.</t>
   </si>
   <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>Withdrawal in progress</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
@@ -337,6 +379,18 @@
   </si>
   <si>
     <t>Collect another {0} to withdraw</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>Record</t>
   </si>
   <si>
     <t>MakeupUIForm.title</t>
@@ -351,7 +405,37 @@
     <t>Balance {0}=$1</t>
   </si>
   <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>Watch ads, get game items from chest.</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>Quitting Now Will Result In The Loss Of One Life Point.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>Quit?</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.privacy</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.quit</t>
+  </si>
+  <si>
+    <t>Quit</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -1321,7 +1405,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1369,15 +1453,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1413,7 +1497,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1421,22 +1505,86 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7731,6 +7879,1650 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7747,1469 +9539,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1073">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1074">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1087">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1088">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1089">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1090">
+            <xdr:cNvPr hidden="1" name="A1" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -9284,18 +9614,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1091">
+            <xdr:cNvPr hidden="1" name="A2" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9370,18 +9700,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1092">
+            <xdr:cNvPr hidden="1" name="A3" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9456,18 +9786,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1093">
+            <xdr:cNvPr hidden="1" name="A4" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9542,18 +9872,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1094">
+            <xdr:cNvPr hidden="1" name="A5" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9628,18 +9958,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1095">
+            <xdr:cNvPr hidden="1" name="A6" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9714,18 +10044,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1096">
+            <xdr:cNvPr hidden="1" name="A7" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9800,18 +10130,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1097">
+            <xdr:cNvPr hidden="1" name="A8" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9886,18 +10216,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1098">
+            <xdr:cNvPr hidden="1" name="A9" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9972,18 +10302,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1099">
+            <xdr:cNvPr hidden="1" name="A10" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -10058,18 +10388,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1100">
+            <xdr:cNvPr hidden="1" name="A11" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -10144,18 +10474,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1101">
+            <xdr:cNvPr hidden="1" name="A12" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10230,18 +10560,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1102">
+            <xdr:cNvPr hidden="1" name="A13" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10316,18 +10646,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1103">
+            <xdr:cNvPr hidden="1" name="A14" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10402,18 +10732,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1104">
+            <xdr:cNvPr hidden="1" name="A15" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10488,18 +10818,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1105">
+            <xdr:cNvPr hidden="1" name="A16" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10574,18 +10904,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1106">
+            <xdr:cNvPr hidden="1" name="A17" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10660,18 +10990,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1107">
+            <xdr:cNvPr hidden="1" name="A18" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10746,18 +11076,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1108">
+            <xdr:cNvPr hidden="1" name="A19" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10832,18 +11162,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1109">
+            <xdr:cNvPr hidden="1" name="A20" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10918,18 +11248,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1110">
+            <xdr:cNvPr hidden="1" name="A21" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -11004,18 +11334,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1111">
+            <xdr:cNvPr hidden="1" name="A22" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -11090,18 +11420,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1112">
+            <xdr:cNvPr hidden="1" name="A23" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -11176,18 +11506,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1113">
+            <xdr:cNvPr hidden="1" name="A24" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11262,18 +11592,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1114">
+            <xdr:cNvPr hidden="1" name="A25" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11348,18 +11678,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1115">
+            <xdr:cNvPr hidden="1" name="A26" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11434,18 +11764,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1116">
+            <xdr:cNvPr hidden="1" name="A27" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11520,18 +11850,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1117">
+            <xdr:cNvPr hidden="1" name="A28" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11606,18 +11936,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1118">
+            <xdr:cNvPr hidden="1" name="A29" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -11692,18 +12022,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1119">
+            <xdr:cNvPr hidden="1" name="A30" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -11778,18 +12108,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1120">
+            <xdr:cNvPr hidden="1" name="A31" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -11864,6 +12194,1468 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A32" id="1121">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1121"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A33" id="1122">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1122"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1123">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1123"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1124">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1124"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A36" id="1125">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1125"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A37" id="1126">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1126"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A38" id="1127">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1127"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A39" id="1128">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1128"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A40" id="1129">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1129"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A41" id="1130">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1130"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A42" id="1131">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1131"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A43" id="1132">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1132"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1133">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1133"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1134">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1134"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1135">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1135"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1136">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1136"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1137">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1137"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -11875,10 +13667,1386 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1121">
+            <xdr:cNvPr hidden="1" name="A49" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1138"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A50" id="1139">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1139"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A51" id="1140">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1140"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A52" id="1141">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1141"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A53" id="1142">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1142"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A54" id="1143">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1143"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A55" id="1144">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1144"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A56" id="1145">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1145"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A57" id="1146">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1146"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A58" id="1147">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1147"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A59" id="1148">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1148"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A60" id="1149">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1149"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A61" id="1150">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1150"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A62" id="1151">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1151"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A63" id="1152">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1152"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1153">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1153"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1154">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -12205,7 +15373,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -12426,232 +15594,376 @@
         <v>45</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="0" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="0" t="s">
+    </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="0" t="s">
         <v>95</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1"/>
+      <c r="B51" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1"/>
+      <c r="B52" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1"/>
+      <c r="B53" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1"/>
+      <c r="B54" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1"/>
+      <c r="B55" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1"/>
+      <c r="B56" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1"/>
+      <c r="B57" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1"/>
+      <c r="B58" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1"/>
+      <c r="B59" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1"/>
+      <c r="B60" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1"/>
+      <c r="B61" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1"/>
+      <c r="B62" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1"/>
+      <c r="B63" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1"/>
+      <c r="B64" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1"/>
+      <c r="B65" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -12664,7 +15976,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1544" name="A1">
+            <control shapeId="1090" r:id="rId1948" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12686,7 +15998,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1545" name="A2">
+            <control shapeId="1091" r:id="rId1949" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12708,7 +16020,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1546" name="A3">
+            <control shapeId="1092" r:id="rId1950" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12730,7 +16042,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1547" name="A4">
+            <control shapeId="1093" r:id="rId1951" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12752,7 +16064,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1548" name="A5">
+            <control shapeId="1094" r:id="rId1952" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12774,7 +16086,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1549" name="A6">
+            <control shapeId="1095" r:id="rId1953" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12796,7 +16108,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1550" name="A7">
+            <control shapeId="1096" r:id="rId1954" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12818,7 +16130,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1551" name="A8">
+            <control shapeId="1097" r:id="rId1955" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12840,7 +16152,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1552" name="A9">
+            <control shapeId="1098" r:id="rId1956" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12862,7 +16174,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1553" name="A10">
+            <control shapeId="1099" r:id="rId1957" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12884,7 +16196,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1554" name="A11">
+            <control shapeId="1100" r:id="rId1958" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12906,7 +16218,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1555" name="A12">
+            <control shapeId="1101" r:id="rId1959" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12928,7 +16240,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1556" name="A13">
+            <control shapeId="1102" r:id="rId1960" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12950,7 +16262,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1557" name="A14">
+            <control shapeId="1103" r:id="rId1961" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12972,7 +16284,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1558" name="A15">
+            <control shapeId="1104" r:id="rId1962" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12994,7 +16306,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1559" name="A16">
+            <control shapeId="1105" r:id="rId1963" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13016,7 +16328,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1560" name="A17">
+            <control shapeId="1106" r:id="rId1964" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13038,7 +16350,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1561" name="A18">
+            <control shapeId="1107" r:id="rId1965" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13060,7 +16372,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1562" name="A19">
+            <control shapeId="1108" r:id="rId1966" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13082,7 +16394,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1563" name="A20">
+            <control shapeId="1109" r:id="rId1967" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13104,7 +16416,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1564" name="A21">
+            <control shapeId="1110" r:id="rId1968" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13126,7 +16438,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1565" name="A22">
+            <control shapeId="1111" r:id="rId1969" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13148,7 +16460,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1566" name="A23">
+            <control shapeId="1112" r:id="rId1970" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13170,7 +16482,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1567" name="A24">
+            <control shapeId="1113" r:id="rId1971" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13192,7 +16504,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1568" name="A25">
+            <control shapeId="1114" r:id="rId1972" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13214,7 +16526,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1569" name="A26">
+            <control shapeId="1115" r:id="rId1973" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13236,7 +16548,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1570" name="A27">
+            <control shapeId="1116" r:id="rId1974" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13258,7 +16570,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1571" name="A28">
+            <control shapeId="1117" r:id="rId1975" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13280,7 +16592,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1572" name="A29">
+            <control shapeId="1118" r:id="rId1976" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13302,7 +16614,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1573" name="A30">
+            <control shapeId="1119" r:id="rId1977" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13324,7 +16636,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1574" name="A31">
+            <control shapeId="1120" r:id="rId1978" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13346,7 +16658,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1575" name="A32">
+            <control shapeId="1121" r:id="rId1979" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13368,7 +16680,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1576" name="A33">
+            <control shapeId="1122" r:id="rId1980" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13390,7 +16702,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1577" name="A34">
+            <control shapeId="1123" r:id="rId1981" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13412,7 +16724,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1578" name="A35">
+            <control shapeId="1124" r:id="rId1982" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13434,7 +16746,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1579" name="A36">
+            <control shapeId="1125" r:id="rId1983" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13456,7 +16768,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1580" name="A37">
+            <control shapeId="1126" r:id="rId1984" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13478,7 +16790,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1581" name="A38">
+            <control shapeId="1127" r:id="rId1985" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13500,7 +16812,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1582" name="A39">
+            <control shapeId="1128" r:id="rId1986" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13522,7 +16834,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1583" name="A40">
+            <control shapeId="1129" r:id="rId1987" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13544,7 +16856,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1584" name="A41">
+            <control shapeId="1130" r:id="rId1988" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13566,7 +16878,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1585" name="A42">
+            <control shapeId="1131" r:id="rId1989" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13588,7 +16900,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1586" name="A43">
+            <control shapeId="1132" r:id="rId1990" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13610,7 +16922,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1587" name="A44">
+            <control shapeId="1133" r:id="rId1991" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13632,7 +16944,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1588" name="A45">
+            <control shapeId="1134" r:id="rId1992" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13654,7 +16966,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1589" name="A46">
+            <control shapeId="1135" r:id="rId1993" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13676,7 +16988,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1590" name="A47">
+            <control shapeId="1136" r:id="rId1994" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13698,7 +17010,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1591" name="A48">
+            <control shapeId="1137" r:id="rId1995" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13720,7 +17032,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1592" name="A49">
+            <control shapeId="1138" r:id="rId1996" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13740,6 +17052,358 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1139" r:id="rId1997" name="A50">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1140" r:id="rId1998" name="A51">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1141" r:id="rId1999" name="A52">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1142" r:id="rId2000" name="A53">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1143" r:id="rId2001" name="A54">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1144" r:id="rId2002" name="A55">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1145" r:id="rId2003" name="A56">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1146" r:id="rId2004" name="A57">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId2005" name="A58">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1148" r:id="rId2006" name="A59">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1149" r:id="rId2007" name="A60">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1150" r:id="rId2008" name="A61">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1151" r:id="rId2009" name="A62">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1152" r:id="rId2010" name="A63">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1153" r:id="rId2011" name="A64">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1154" r:id="rId2012" name="A65">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -207,6 +207,9 @@
     <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
   </si>
   <si>
+    <t>claim</t>
+  </si>
+  <si>
     <t>CoinRewardUIForm.titletxt</t>
   </si>
   <si>
@@ -327,16 +330,19 @@
     <t>Payment information saved successfully</t>
   </si>
   <si>
-    <t>LevelCompleteUIForm.complete</t>
+    <t>level</t>
   </si>
   <si>
     <t>Level {0}</t>
   </si>
   <si>
-    <t>LevelCompleteUIForm.leveltxt</t>
+    <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
-    <t>Completed</t>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>Next</t>
   </si>
   <si>
     <t>MakeUpFail</t>
@@ -409,9 +415,6 @@
   </si>
   <si>
     <t>Watch ads, get game items from chest.</t>
-  </si>
-  <si>
-    <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
     <t>QuitConfirmUIForm.desc</t>
@@ -1409,7 +1412,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1453,7 +1456,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1465,7 +1468,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1497,19 +1500,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1521,27 +1524,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1588,6 +1591,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -1602,6 +1609,1066 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -9539,179 +10606,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1090">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1091">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1092">
+            <xdr:cNvPr hidden="1" name="A1" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9786,18 +10681,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1093">
+            <xdr:cNvPr hidden="1" name="A2" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9872,18 +10767,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1094">
+            <xdr:cNvPr hidden="1" name="A3" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9958,18 +10853,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1095">
+            <xdr:cNvPr hidden="1" name="A4" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -10044,18 +10939,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1096">
+            <xdr:cNvPr hidden="1" name="A5" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -10130,18 +11025,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1097">
+            <xdr:cNvPr hidden="1" name="A6" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -10216,18 +11111,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1098">
+            <xdr:cNvPr hidden="1" name="A7" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -10302,18 +11197,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1099">
+            <xdr:cNvPr hidden="1" name="A8" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -10388,18 +11283,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1100">
+            <xdr:cNvPr hidden="1" name="A9" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -10474,18 +11369,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1101">
+            <xdr:cNvPr hidden="1" name="A10" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10560,18 +11455,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1102">
+            <xdr:cNvPr hidden="1" name="A11" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10646,18 +11541,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1103">
+            <xdr:cNvPr hidden="1" name="A12" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10732,18 +11627,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1104">
+            <xdr:cNvPr hidden="1" name="A13" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10818,18 +11713,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1105">
+            <xdr:cNvPr hidden="1" name="A14" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10904,18 +11799,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1106">
+            <xdr:cNvPr hidden="1" name="A15" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10990,18 +11885,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1107">
+            <xdr:cNvPr hidden="1" name="A16" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -11076,18 +11971,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1108">
+            <xdr:cNvPr hidden="1" name="A17" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -11162,18 +12057,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1109">
+            <xdr:cNvPr hidden="1" name="A18" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -11248,18 +12143,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1110">
+            <xdr:cNvPr hidden="1" name="A19" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -11334,18 +12229,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1111">
+            <xdr:cNvPr hidden="1" name="A20" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -11420,18 +12315,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1112">
+            <xdr:cNvPr hidden="1" name="A21" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -11506,18 +12401,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1113">
+            <xdr:cNvPr hidden="1" name="A22" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11592,18 +12487,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1114">
+            <xdr:cNvPr hidden="1" name="A23" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11678,18 +12573,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1115">
+            <xdr:cNvPr hidden="1" name="A24" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11764,18 +12659,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1116">
+            <xdr:cNvPr hidden="1" name="A25" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11850,18 +12745,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1117">
+            <xdr:cNvPr hidden="1" name="A26" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11936,18 +12831,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1118">
+            <xdr:cNvPr hidden="1" name="A27" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -12022,18 +12917,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1119">
+            <xdr:cNvPr hidden="1" name="A28" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -12108,18 +13003,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1120">
+            <xdr:cNvPr hidden="1" name="A29" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -12194,18 +13089,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1121">
+            <xdr:cNvPr hidden="1" name="A30" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1121"/>
@@ -12280,18 +13175,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1122">
+            <xdr:cNvPr hidden="1" name="A31" id="1122">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1122"/>
@@ -12366,18 +13261,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1123">
+            <xdr:cNvPr hidden="1" name="A32" id="1123">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1123"/>
@@ -12452,18 +13347,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1124">
+            <xdr:cNvPr hidden="1" name="A33" id="1124">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1124"/>
@@ -12538,18 +13433,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1125">
+            <xdr:cNvPr hidden="1" name="A34" id="1125">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1125"/>
@@ -12624,18 +13519,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1126">
+            <xdr:cNvPr hidden="1" name="A35" id="1126">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1126"/>
@@ -12710,18 +13605,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1127">
+            <xdr:cNvPr hidden="1" name="A36" id="1127">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1127"/>
@@ -12796,18 +13691,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1128">
+            <xdr:cNvPr hidden="1" name="A37" id="1128">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1128"/>
@@ -12882,18 +13777,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1129">
+            <xdr:cNvPr hidden="1" name="A38" id="1129">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1129"/>
@@ -12968,18 +13863,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1130">
+            <xdr:cNvPr hidden="1" name="A39" id="1130">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1130"/>
@@ -13054,18 +13949,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1131">
+            <xdr:cNvPr hidden="1" name="A40" id="1131">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1131"/>
@@ -13140,18 +14035,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1132">
+            <xdr:cNvPr hidden="1" name="A41" id="1132">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1132"/>
@@ -13226,18 +14121,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1133">
+            <xdr:cNvPr hidden="1" name="A42" id="1133">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1133"/>
@@ -13312,18 +14207,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1134">
+            <xdr:cNvPr hidden="1" name="A43" id="1134">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1134"/>
@@ -13398,18 +14293,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1135">
+            <xdr:cNvPr hidden="1" name="A44" id="1135">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1135"/>
@@ -13484,18 +14379,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1136">
+            <xdr:cNvPr hidden="1" name="A45" id="1136">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1136"/>
@@ -13570,18 +14465,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1137">
+            <xdr:cNvPr hidden="1" name="A46" id="1137">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1137"/>
@@ -13656,18 +14551,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1138">
+            <xdr:cNvPr hidden="1" name="A47" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1138"/>
@@ -13742,18 +14637,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1139">
+            <xdr:cNvPr hidden="1" name="A48" id="1139">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1139"/>
@@ -13828,18 +14723,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1140">
+            <xdr:cNvPr hidden="1" name="A49" id="1140">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1140"/>
@@ -13914,18 +14809,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1141">
+            <xdr:cNvPr hidden="1" name="A50" id="1141">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1141"/>
@@ -14000,18 +14895,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1142">
+            <xdr:cNvPr hidden="1" name="A51" id="1142">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1142"/>
@@ -14086,18 +14981,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1143">
+            <xdr:cNvPr hidden="1" name="A52" id="1143">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1143"/>
@@ -14172,18 +15067,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1144">
+            <xdr:cNvPr hidden="1" name="A53" id="1144">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1144"/>
@@ -14258,18 +15153,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1145">
+            <xdr:cNvPr hidden="1" name="A54" id="1145">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1145"/>
@@ -14344,18 +15239,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1146">
+            <xdr:cNvPr hidden="1" name="A55" id="1146">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1146"/>
@@ -14430,18 +15325,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1147">
+            <xdr:cNvPr hidden="1" name="A56" id="1147">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1147"/>
@@ -14516,18 +15411,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1148">
+            <xdr:cNvPr hidden="1" name="A57" id="1148">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1148"/>
@@ -14602,18 +15497,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1149">
+            <xdr:cNvPr hidden="1" name="A58" id="1149">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1149"/>
@@ -14688,18 +15583,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1150">
+            <xdr:cNvPr hidden="1" name="A59" id="1150">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1150"/>
@@ -14774,18 +15669,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1151">
+            <xdr:cNvPr hidden="1" name="A60" id="1151">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1151"/>
@@ -14860,18 +15755,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1152">
+            <xdr:cNvPr hidden="1" name="A61" id="1152">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1152"/>
@@ -14946,18 +15841,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1153">
+            <xdr:cNvPr hidden="1" name="A62" id="1153">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1153"/>
@@ -15032,6 +15927,178 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A63" id="1154">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1155">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1155"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>64</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -15043,10 +16110,96 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1154">
+            <xdr:cNvPr hidden="1" name="A65" id="1156">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1156"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A66" id="1157">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1157"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -15373,7 +16526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -15594,7 +16747,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -15603,97 +16756,97 @@
         <v>46</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
@@ -15702,241 +16855,241 @@
         <v>67</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1"/>
       <c r="B50" s="0" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1"/>
       <c r="B51" s="0" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1"/>
       <c r="B52" s="0" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1"/>
       <c r="B53" s="0" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1"/>
       <c r="B54" s="0" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1"/>
       <c r="B55" s="0" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1"/>
       <c r="B56" s="0" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1"/>
       <c r="B57" s="0" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1"/>
       <c r="B58" s="0" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1"/>
       <c r="B59" s="0" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1"/>
       <c r="B60" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1"/>
       <c r="B61" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1"/>
       <c r="B62" s="0" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63">
@@ -15945,7 +17098,7 @@
         <v>119</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -15954,16 +17107,25 @@
         <v>120</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1"/>
       <c r="B65" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C65" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="0" t="s">
+    </row>
+    <row r="66">
+      <c r="A66" s="1"/>
+      <c r="B66" s="0" t="s">
         <v>123</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -15976,7 +17138,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1948" name="A1">
+            <control shapeId="1092" r:id="rId2209" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15998,7 +17160,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1949" name="A2">
+            <control shapeId="1093" r:id="rId2210" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16020,7 +17182,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1950" name="A3">
+            <control shapeId="1094" r:id="rId2211" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16042,7 +17204,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1951" name="A4">
+            <control shapeId="1095" r:id="rId2212" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16064,7 +17226,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1952" name="A5">
+            <control shapeId="1096" r:id="rId2213" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16086,7 +17248,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1953" name="A6">
+            <control shapeId="1097" r:id="rId2214" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16108,7 +17270,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1954" name="A7">
+            <control shapeId="1098" r:id="rId2215" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16130,7 +17292,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1955" name="A8">
+            <control shapeId="1099" r:id="rId2216" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16152,7 +17314,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1956" name="A9">
+            <control shapeId="1100" r:id="rId2217" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16174,7 +17336,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1957" name="A10">
+            <control shapeId="1101" r:id="rId2218" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16196,7 +17358,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1958" name="A11">
+            <control shapeId="1102" r:id="rId2219" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16218,7 +17380,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1959" name="A12">
+            <control shapeId="1103" r:id="rId2220" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16240,7 +17402,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1960" name="A13">
+            <control shapeId="1104" r:id="rId2221" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16262,7 +17424,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1961" name="A14">
+            <control shapeId="1105" r:id="rId2222" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16284,7 +17446,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1962" name="A15">
+            <control shapeId="1106" r:id="rId2223" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16306,7 +17468,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1963" name="A16">
+            <control shapeId="1107" r:id="rId2224" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16328,7 +17490,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1964" name="A17">
+            <control shapeId="1108" r:id="rId2225" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16350,7 +17512,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1965" name="A18">
+            <control shapeId="1109" r:id="rId2226" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16372,7 +17534,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1966" name="A19">
+            <control shapeId="1110" r:id="rId2227" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16394,7 +17556,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1967" name="A20">
+            <control shapeId="1111" r:id="rId2228" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16416,7 +17578,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1968" name="A21">
+            <control shapeId="1112" r:id="rId2229" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16438,7 +17600,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1969" name="A22">
+            <control shapeId="1113" r:id="rId2230" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16460,7 +17622,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1970" name="A23">
+            <control shapeId="1114" r:id="rId2231" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16482,7 +17644,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1971" name="A24">
+            <control shapeId="1115" r:id="rId2232" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16504,7 +17666,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1972" name="A25">
+            <control shapeId="1116" r:id="rId2233" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16526,7 +17688,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1973" name="A26">
+            <control shapeId="1117" r:id="rId2234" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16548,7 +17710,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1974" name="A27">
+            <control shapeId="1118" r:id="rId2235" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16570,7 +17732,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1975" name="A28">
+            <control shapeId="1119" r:id="rId2236" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16592,7 +17754,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1976" name="A29">
+            <control shapeId="1120" r:id="rId2237" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16614,7 +17776,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1977" name="A30">
+            <control shapeId="1121" r:id="rId2238" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16636,7 +17798,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1978" name="A31">
+            <control shapeId="1122" r:id="rId2239" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16658,7 +17820,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1979" name="A32">
+            <control shapeId="1123" r:id="rId2240" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16680,7 +17842,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1980" name="A33">
+            <control shapeId="1124" r:id="rId2241" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16702,7 +17864,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1981" name="A34">
+            <control shapeId="1125" r:id="rId2242" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16724,7 +17886,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1982" name="A35">
+            <control shapeId="1126" r:id="rId2243" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16746,7 +17908,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1983" name="A36">
+            <control shapeId="1127" r:id="rId2244" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16768,7 +17930,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1984" name="A37">
+            <control shapeId="1128" r:id="rId2245" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16790,7 +17952,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1985" name="A38">
+            <control shapeId="1129" r:id="rId2246" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16812,7 +17974,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1986" name="A39">
+            <control shapeId="1130" r:id="rId2247" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16834,7 +17996,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1987" name="A40">
+            <control shapeId="1131" r:id="rId2248" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16856,7 +18018,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1988" name="A41">
+            <control shapeId="1132" r:id="rId2249" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16878,7 +18040,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1989" name="A42">
+            <control shapeId="1133" r:id="rId2250" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16900,7 +18062,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1990" name="A43">
+            <control shapeId="1134" r:id="rId2251" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16922,7 +18084,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1991" name="A44">
+            <control shapeId="1135" r:id="rId2252" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16944,7 +18106,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1992" name="A45">
+            <control shapeId="1136" r:id="rId2253" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16966,7 +18128,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1993" name="A46">
+            <control shapeId="1137" r:id="rId2254" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16988,7 +18150,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1994" name="A47">
+            <control shapeId="1138" r:id="rId2255" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17010,7 +18172,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1995" name="A48">
+            <control shapeId="1139" r:id="rId2256" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17032,7 +18194,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1996" name="A49">
+            <control shapeId="1140" r:id="rId2257" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17054,7 +18216,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId1997" name="A50">
+            <control shapeId="1141" r:id="rId2258" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17076,7 +18238,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId1998" name="A51">
+            <control shapeId="1142" r:id="rId2259" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17098,7 +18260,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId1999" name="A52">
+            <control shapeId="1143" r:id="rId2260" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17120,7 +18282,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId2000" name="A53">
+            <control shapeId="1144" r:id="rId2261" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17142,7 +18304,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId2001" name="A54">
+            <control shapeId="1145" r:id="rId2262" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17164,7 +18326,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId2002" name="A55">
+            <control shapeId="1146" r:id="rId2263" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17186,7 +18348,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId2003" name="A56">
+            <control shapeId="1147" r:id="rId2264" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17208,7 +18370,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId2004" name="A57">
+            <control shapeId="1148" r:id="rId2265" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17230,7 +18392,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId2005" name="A58">
+            <control shapeId="1149" r:id="rId2266" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17252,7 +18414,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId2006" name="A59">
+            <control shapeId="1150" r:id="rId2267" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17274,7 +18436,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId2007" name="A60">
+            <control shapeId="1151" r:id="rId2268" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17296,7 +18458,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId2008" name="A61">
+            <control shapeId="1152" r:id="rId2269" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17318,7 +18480,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId2009" name="A62">
+            <control shapeId="1153" r:id="rId2270" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17340,7 +18502,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId2010" name="A63">
+            <control shapeId="1154" r:id="rId2271" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17362,7 +18524,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId2011" name="A64">
+            <control shapeId="1155" r:id="rId2272" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17384,7 +18546,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId2012" name="A65">
+            <control shapeId="1156" r:id="rId2273" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -17404,6 +18566,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1157" r:id="rId2274" name="A66">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -140,7 +140,7 @@
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
-    <t>Redeem</t>
+    <t>Cash out</t>
   </si>
   <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>Win {0} levels!</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm.title</t>
   </si>
 </sst>
 </file>
@@ -683,6 +686,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6373,12 +6380,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A67" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6913,6 +7006,14 @@
       </c>
       <c r="C66" s="1" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -8374,6 +8475,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1091" r:id="rId69" name="A67">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -281,6 +281,9 @@
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -390,6 +393,69 @@
   </si>
   <si>
     <t>MakeupRecordUIForm.title</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Extra Lives</t>
+  </si>
+  <si>
+    <t>AddPropUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Rocket</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm.loading</t>
+  </si>
+  <si>
+    <t>Loading...</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quit</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.avatarTxt</t>
+  </si>
+  <si>
+    <t>Select an avatar:</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterDesc</t>
+  </si>
+  <si>
+    <t>Enter your PayPal account</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterAgainDesc</t>
+  </si>
+  <si>
+    <t>Enter the paypal account again</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.confirm</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>TaskItem.adTxt</t>
+  </si>
+  <si>
+    <t>Watch an AD!</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>TaskItem.go</t>
+  </si>
+  <si>
+    <t>Go</t>
   </si>
 </sst>
 </file>
@@ -690,7 +756,51 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6466,12 +6576,958 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A68" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A70" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A71" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A72" id="1096">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A73" id="1097">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A74" id="1098">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A75" id="1099">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1099"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A76" id="1100">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1100"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A77" id="1101">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1101"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A78" id="1102">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1102"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6853,132 +7909,132 @@
         <v>88</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -6986,7 +8042,7 @@
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -6994,26 +8050,114 @@
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -8497,6 +9641,248 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1092" r:id="rId70" name="A68">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId72" name="A70">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId73" name="A71">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1096" r:id="rId74" name="A72">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1097" r:id="rId75" name="A73">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1098" r:id="rId76" name="A74">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1099" r:id="rId77" name="A75">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1100" r:id="rId78" name="A76">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1101" r:id="rId79" name="A77">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1102" r:id="rId80" name="A78">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -456,6 +456,15 @@
   </si>
   <si>
     <t>Go</t>
+  </si>
+  <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>You need to pass {0} levels and collect {1} Reaching Balance before you can claim it.</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
   </si>
 </sst>
 </file>
@@ -804,7 +813,15 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7522,12 +7539,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A79" id="1103">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1103"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A80" id="1104">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1104"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8158,6 +8347,22 @@
       </c>
       <c r="C78" s="1" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -9883,6 +10088,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1103" r:id="rId81" name="A79">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1104" r:id="rId82" name="A80">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -188,7 +188,7 @@
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>Tap to Move</t>
+    <t>Tap that item and let the cannon fly!</t>
   </si>
   <si>
     <t>GuidTxt3</t>
@@ -465,6 +465,42 @@
   </si>
   <si>
     <t>MakeupItem.cashout</t>
+  </si>
+  <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
+    <t>Clear every item before you run out of shots!</t>
+  </si>
+  <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>Today`s Bonus Pool</t>
+  </si>
+  <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>Tap the items on the table</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>Reaching Balance</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>Select Booster:</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>Thank you for your generous donation!</t>
   </si>
 </sst>
 </file>
@@ -610,19 +646,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -825,6 +861,30 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7711,12 +7771,528 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A81" id="1105">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1105"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A82" id="1106">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1106"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A83" id="1107">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1107"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A84" id="1108">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1108"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A85" id="1109">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1109"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>86</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A86" id="1110">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1110"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8363,6 +8939,54 @@
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -10132,6 +10756,138 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1105" r:id="rId83" name="A81">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1106" r:id="rId84" name="A82">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1107" r:id="rId85" name="A83">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1108" r:id="rId86" name="A84">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1109" r:id="rId87" name="A85">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1110" r:id="rId88" name="A86">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>86</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -26,24 +26,6 @@
     <t>Continue?</t>
   </si>
   <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
-  </si>
-  <si>
-    <t>Win Streak Challenge Failing</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.restart</t>
-  </si>
-  <si>
-    <t>Restart</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>Revive</t>
-  </si>
-  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
@@ -56,325 +38,244 @@
     <t>Claim</t>
   </si>
   <si>
-    <t>ArrowRewardDialogUIForm.Continue</t>
+    <t>ArrowRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Congratulations</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.OFF</t>
+  </si>
+  <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.ON</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>ArrowUITopbar.cashOut</t>
+  </si>
+  <si>
+    <t>Cash out</t>
+  </si>
+  <si>
+    <t>ArrowWithdrawalInfoItem.infoTxt</t>
+  </si>
+  <si>
+    <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Enteraccountnumber</t>
+  </si>
+  <si>
+    <t>Enter your account</t>
+  </si>
+  <si>
+    <t>EnterCPF</t>
+  </si>
+  <si>
+    <t>Enter CPF</t>
+  </si>
+  <si>
+    <t>Enteremail</t>
+  </si>
+  <si>
+    <t>Confirm email</t>
+  </si>
+  <si>
+    <t>EnterFullName</t>
+  </si>
+  <si>
+    <t>Enter Full Name</t>
+  </si>
+  <si>
+    <t>EnterPayPalaccount</t>
+  </si>
+  <si>
+    <t>Enter PayPal account</t>
+  </si>
+  <si>
+    <t>GuidTxt1</t>
+  </si>
+  <si>
+    <t>Tap that item and let the cannon fly!</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>InfoErrTips1</t>
+  </si>
+  <si>
+    <t>Please enter a valid email address</t>
+  </si>
+  <si>
+    <t>InfoErrTips2</t>
+  </si>
+  <si>
+    <t>Please enter a valid CPF</t>
+  </si>
+  <si>
+    <t>InfoErrTips3</t>
+  </si>
+  <si>
+    <t>PayPal account must be a valid email</t>
+  </si>
+  <si>
+    <t>InfoErrTips4</t>
+  </si>
+  <si>
+    <t>Please enter your full name</t>
+  </si>
+  <si>
+    <t>InfoErrTips5</t>
+  </si>
+  <si>
+    <t>Please enter your account number</t>
+  </si>
+  <si>
+    <t>InfoErrTips6</t>
+  </si>
+  <si>
+    <t>Please select a payment method</t>
+  </si>
+  <si>
+    <t>InfoErrTips7</t>
+  </si>
+  <si>
+    <t>Payment information saved successfully</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>Level {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>Next</t>
+  </si>
+  <si>
+    <t>MakeUpFail</t>
+  </si>
+  <si>
+    <t>We regret that the exchange has failed.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>Please ensure that the PayPal account entered twice is consistent.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>Please enter the correct email format.</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>Withdrawal in progress</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
+    <t>MakeUpStep1</t>
+  </si>
+  <si>
+    <t>Pass level {0} to withdraw</t>
+  </si>
+  <si>
+    <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>Collect another {0} to withdraw</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>Cash Out</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>Balance {0}=$1</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>Watch ads, get game items from chest.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>Quitting Now Will Result In The Loss Of One Life Point.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>Quit?</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>Continue</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.NextLevel</t>
-  </si>
-  <si>
-    <t>Next Level</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Combo rewards</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.winTitle</t>
-  </si>
-  <si>
-    <t>LEVEL COMPLETE</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Congratulations</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.OFF</t>
-  </si>
-  <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.ON</t>
-  </si>
-  <si>
-    <t>on</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Home</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Music</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Privacy</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Resume</t>
-  </si>
-  <si>
-    <t>Resume</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Sound</t>
-  </si>
-  <si>
-    <t>Sound</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Text_Title</t>
-  </si>
-  <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Vibrate</t>
-  </si>
-  <si>
-    <t>Vibrate</t>
-  </si>
-  <si>
-    <t>ArrowUITopbar.cashOut</t>
-  </si>
-  <si>
-    <t>Cash out</t>
-  </si>
-  <si>
-    <t>ArrowWithdrawalInfoItem.infoTxt</t>
-  </si>
-  <si>
-    <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
-  </si>
-  <si>
-    <t>claim</t>
-  </si>
-  <si>
-    <t>CoinRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Enteraccountnumber</t>
-  </si>
-  <si>
-    <t>Enter your account</t>
-  </si>
-  <si>
-    <t>EnterCPF</t>
-  </si>
-  <si>
-    <t>Enter CPF</t>
-  </si>
-  <si>
-    <t>Enteremail</t>
-  </si>
-  <si>
-    <t>Confirm email</t>
-  </si>
-  <si>
-    <t>EnterFullName</t>
-  </si>
-  <si>
-    <t>Enter Full Name</t>
-  </si>
-  <si>
-    <t>EnterPayPalaccount</t>
-  </si>
-  <si>
-    <t>Enter PayPal account</t>
-  </si>
-  <si>
-    <t>GuidTxt1</t>
-  </si>
-  <si>
-    <t>Tap that item and let the cannon fly!</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click here to cash out </t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>Spread Fingers to Zoom</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please find your current balance here. </t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
-  </si>
-  <si>
-    <t>Complete requirements to cash out.</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.home</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.setting</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.task</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>InfoErrTips1</t>
-  </si>
-  <si>
-    <t>Please enter a valid email address</t>
-  </si>
-  <si>
-    <t>InfoErrTips2</t>
-  </si>
-  <si>
-    <t>Please enter a valid CPF</t>
-  </si>
-  <si>
-    <t>InfoErrTips3</t>
-  </si>
-  <si>
-    <t>PayPal account must be a valid email</t>
-  </si>
-  <si>
-    <t>InfoErrTips4</t>
-  </si>
-  <si>
-    <t>Please enter your full name</t>
-  </si>
-  <si>
-    <t>InfoErrTips5</t>
-  </si>
-  <si>
-    <t>Please enter your account number</t>
-  </si>
-  <si>
-    <t>InfoErrTips6</t>
-  </si>
-  <si>
-    <t>Please select a payment method</t>
-  </si>
-  <si>
-    <t>InfoErrTips7</t>
-  </si>
-  <si>
-    <t>Payment information saved successfully</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Level {0}</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.complete</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.next</t>
-  </si>
-  <si>
-    <t>Next</t>
-  </si>
-  <si>
-    <t>MakeUpFail</t>
-  </si>
-  <si>
-    <t>We regret that the exchange has failed.</t>
-  </si>
-  <si>
-    <t>makeupInfoHint1</t>
-  </si>
-  <si>
-    <t>Please ensure that the PayPal account entered twice is consistent.</t>
-  </si>
-  <si>
-    <t>makeupInfoHint2</t>
-  </si>
-  <si>
-    <t>Please enter the correct email format.</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>Withdrawal in progress</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Payment Method</t>
-  </si>
-  <si>
-    <t>MakeUpStep1</t>
-  </si>
-  <si>
-    <t>Pass level {0} to withdraw</t>
-  </si>
-  <si>
-    <t>MakeUpStep2</t>
-  </si>
-  <si>
-    <t>Collect another {0} to withdraw</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.input</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.record</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t>Cash Out</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.txtBalance</t>
-  </si>
-  <si>
-    <t>Balance {0}=$1</t>
-  </si>
-  <si>
-    <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>Watch ads, get game items from chest.</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.desc</t>
-  </si>
-  <si>
-    <t>Quitting Now Will Result In The Loss Of One Life Point.</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.quitTxt</t>
-  </si>
-  <si>
-    <t>Quit?</t>
-  </si>
-  <si>
-    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>SettingPageUIForm.privacy</t>
@@ -558,27 +459,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -598,23 +499,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,7 +531,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,7 +539,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -646,11 +547,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -662,11 +563,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -674,7 +575,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -682,31 +583,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -718,7 +619,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,11 +627,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
@@ -742,11 +643,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -774,7 +675,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -782,7 +683,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
@@ -805,83 +706,11 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6739,1560 +6568,12 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1093">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A71" id="1095">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A72" id="1096">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A73" id="1097">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A74" id="1098">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A75" id="1099">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A76" id="1100">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A77" id="1101">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A78" id="1102">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A79" id="1103">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A80" id="1104">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A81" id="1105">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A82" id="1106">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A83" id="1107">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A84" id="1108">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A85" id="1109">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>86</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A86" id="1110">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8378,119 +6659,119 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -8498,199 +6779,199 @@
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -8722,95 +7003,95 @@
         <v>100</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -8834,159 +7115,15 @@
         <v>126</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -10492,402 +8629,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId71" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId72" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId73" name="A71">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId74" name="A72">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId75" name="A73">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId76" name="A74">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId77" name="A75">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId78" name="A76">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId79" name="A77">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId80" name="A78">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId81" name="A79">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId82" name="A80">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId83" name="A81">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId84" name="A82">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId85" name="A83">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId86" name="A84">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId87" name="A85">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId88" name="A86">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>86</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>Thank you for your generous donation!</t>
+  </si>
+  <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>Collect treasure chests</t>
   </si>
 </sst>
 </file>
@@ -706,6 +712,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6568,12 +6578,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -7124,6 +7220,14 @@
       </c>
       <c r="C68" s="1" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -8629,6 +8733,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>
